--- a/output/Data and Chart Outputs/texas_production_forecast.xlsx
+++ b/output/Data and Chart Outputs/texas_production_forecast.xlsx
@@ -585,12 +585,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Permian cap'!$A$2:$A$85</f>
+              <f>'Chart - Permian cap'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Permian cap'!$B$2:$B$85</f>
+              <f>'Chart - Permian cap'!$B$2:$B$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -621,12 +621,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Permian cap'!$A$2:$A$85</f>
+              <f>'Chart - Permian cap'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Permian cap'!$C$2:$C$85</f>
+              <f>'Chart - Permian cap'!$C$2:$C$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -657,12 +657,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Permian cap'!$A$2:$A$85</f>
+              <f>'Chart - Permian cap'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Permian cap'!$D$2:$D$85</f>
+              <f>'Chart - Permian cap'!$D$2:$D$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -695,8 +695,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="7"/>
-        <tickMarkSkip val="7"/>
+        <tickLblSkip val="4"/>
+        <tickMarkSkip val="4"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2993,7 +2993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3023,7 +3023,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>44562</v>
+        <v>45658</v>
+      </c>
+      <c r="B2" t="n">
+        <v>25.8656134</v>
       </c>
       <c r="C2" t="n">
         <v>29.5</v>
@@ -3034,7 +3037,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>44593</v>
+        <v>45689</v>
+      </c>
+      <c r="B3" t="n">
+        <v>26.25359514</v>
       </c>
       <c r="C3" t="n">
         <v>29.5</v>
@@ -3045,7 +3051,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>44621</v>
+        <v>45717</v>
+      </c>
+      <c r="B4" t="n">
+        <v>26.90295259</v>
       </c>
       <c r="C4" t="n">
         <v>29.5</v>
@@ -3056,7 +3065,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>44652</v>
+        <v>45748</v>
+      </c>
+      <c r="B5" t="n">
+        <v>26.86164757</v>
       </c>
       <c r="C5" t="n">
         <v>29.5</v>
@@ -3067,7 +3079,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>44682</v>
+        <v>45778</v>
+      </c>
+      <c r="B6" t="n">
+        <v>26.87649226</v>
       </c>
       <c r="C6" t="n">
         <v>29.5</v>
@@ -3078,7 +3093,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>44713</v>
+        <v>45809</v>
+      </c>
+      <c r="B7" t="n">
+        <v>27.44590982</v>
       </c>
       <c r="C7" t="n">
         <v>29.5</v>
@@ -3089,7 +3107,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>44743</v>
+        <v>45839</v>
+      </c>
+      <c r="B8" t="n">
+        <v>28.09928137</v>
       </c>
       <c r="C8" t="n">
         <v>29.5</v>
@@ -3100,7 +3121,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>44774</v>
+        <v>45870</v>
+      </c>
+      <c r="B9" t="n">
+        <v>28.34933697</v>
       </c>
       <c r="C9" t="n">
         <v>29.5</v>
@@ -3111,7 +3135,10 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>44805</v>
+        <v>45901</v>
+      </c>
+      <c r="B10" t="n">
+        <v>28.48629962</v>
       </c>
       <c r="C10" t="n">
         <v>29.5</v>
@@ -3122,7 +3149,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>44835</v>
+        <v>45931</v>
+      </c>
+      <c r="B11" t="n">
+        <v>27.75974445</v>
       </c>
       <c r="C11" t="n">
         <v>29.5</v>
@@ -3133,7 +3163,10 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>44866</v>
+        <v>45962</v>
+      </c>
+      <c r="B12" t="n">
+        <v>28.68153881</v>
       </c>
       <c r="C12" t="n">
         <v>29.5</v>
@@ -3144,7 +3177,10 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>44896</v>
+        <v>45992</v>
+      </c>
+      <c r="B13" t="n">
+        <v>28.91912698</v>
       </c>
       <c r="C13" t="n">
         <v>29.5</v>
@@ -3155,7 +3191,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>44927</v>
+        <v>46023</v>
+      </c>
+      <c r="B14" t="n">
+        <v>27.92296452</v>
       </c>
       <c r="C14" t="n">
         <v>29.5</v>
@@ -3166,7 +3205,10 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>44958</v>
+        <v>46054</v>
+      </c>
+      <c r="B15" t="n">
+        <v>28.93248373</v>
       </c>
       <c r="C15" t="n">
         <v>29.5</v>
@@ -3177,7 +3219,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>44986</v>
+        <v>46082</v>
+      </c>
+      <c r="B16" t="n">
+        <v>28.84765075</v>
       </c>
       <c r="C16" t="n">
         <v>29.5</v>
@@ -3188,7 +3233,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>45017</v>
+        <v>46113</v>
+      </c>
+      <c r="B17" t="n">
+        <v>28.96837335</v>
       </c>
       <c r="C17" t="n">
         <v>29.5</v>
@@ -3199,7 +3247,10 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>45047</v>
+        <v>46143</v>
+      </c>
+      <c r="B18" t="n">
+        <v>28.96428488</v>
       </c>
       <c r="C18" t="n">
         <v>29.5</v>
@@ -3210,7 +3261,10 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>45078</v>
+        <v>46174</v>
+      </c>
+      <c r="B19" t="n">
+        <v>29.45638012</v>
       </c>
       <c r="C19" t="n">
         <v>29.5</v>
@@ -3221,10 +3275,13 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>45108</v>
+        <v>46204</v>
+      </c>
+      <c r="B20" t="n">
+        <v>29.56494646</v>
       </c>
       <c r="C20" t="n">
-        <v>29.5</v>
+        <v>30.07</v>
       </c>
       <c r="D20" t="n">
         <v>29.5</v>
@@ -3232,10 +3289,13 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45139</v>
+        <v>46235</v>
+      </c>
+      <c r="B21" t="n">
+        <v>29.65626961</v>
       </c>
       <c r="C21" t="n">
-        <v>29.5</v>
+        <v>30.07</v>
       </c>
       <c r="D21" t="n">
         <v>29.5</v>
@@ -3243,10 +3303,13 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45170</v>
+        <v>46266</v>
+      </c>
+      <c r="B22" t="n">
+        <v>29.69343155</v>
       </c>
       <c r="C22" t="n">
-        <v>29.5</v>
+        <v>30.07</v>
       </c>
       <c r="D22" t="n">
         <v>29.5</v>
@@ -3254,10 +3317,13 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45200</v>
+        <v>46296</v>
+      </c>
+      <c r="B23" t="n">
+        <v>29.70331723</v>
       </c>
       <c r="C23" t="n">
-        <v>29.5</v>
+        <v>32.57</v>
       </c>
       <c r="D23" t="n">
         <v>29.5</v>
@@ -3265,10 +3331,13 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45231</v>
+        <v>46327</v>
+      </c>
+      <c r="B24" t="n">
+        <v>29.79495856</v>
       </c>
       <c r="C24" t="n">
-        <v>29.5</v>
+        <v>32.57</v>
       </c>
       <c r="D24" t="n">
         <v>29.5</v>
@@ -3276,10 +3345,13 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45261</v>
+        <v>46357</v>
+      </c>
+      <c r="B25" t="n">
+        <v>29.99115633</v>
       </c>
       <c r="C25" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
       <c r="D25" t="n">
         <v>29.5</v>
@@ -3287,841 +3359,337 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45292</v>
+        <v>46388</v>
       </c>
       <c r="B26" t="n">
-        <v>22.59695542</v>
+        <v>29.80984683</v>
       </c>
       <c r="C26" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
       <c r="D26" t="n">
-        <v>29.5</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45323</v>
+        <v>46419</v>
       </c>
       <c r="B27" t="n">
-        <v>23.68395313</v>
+        <v>30.22305925</v>
       </c>
       <c r="C27" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
       <c r="D27" t="n">
-        <v>29.5</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45352</v>
+        <v>46447</v>
       </c>
       <c r="B28" t="n">
-        <v>24.05521084</v>
+        <v>30.7157843</v>
       </c>
       <c r="C28" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
       <c r="D28" t="n">
-        <v>29.5</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>45383</v>
+        <v>46478</v>
       </c>
       <c r="B29" t="n">
-        <v>24.10201897</v>
+        <v>30.96319057</v>
       </c>
       <c r="C29" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
       <c r="D29" t="n">
-        <v>29.5</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>45413</v>
+        <v>46508</v>
       </c>
       <c r="B30" t="n">
-        <v>24.28678653</v>
+        <v>31.21276197</v>
       </c>
       <c r="C30" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
       <c r="D30" t="n">
-        <v>29.5</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>45444</v>
+        <v>46539</v>
       </c>
       <c r="B31" t="n">
-        <v>24.9598424</v>
+        <v>31.45953397</v>
       </c>
       <c r="C31" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
       <c r="D31" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>45474</v>
+        <v>46569</v>
       </c>
       <c r="B32" t="n">
-        <v>25.3119424</v>
+        <v>31.70434641</v>
       </c>
       <c r="C32" t="n">
-        <v>29.5</v>
+        <v>34.77</v>
       </c>
       <c r="D32" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>45505</v>
+        <v>46600</v>
       </c>
       <c r="B33" t="n">
-        <v>25.74684842</v>
+        <v>31.9460196</v>
       </c>
       <c r="C33" t="n">
-        <v>29.5</v>
+        <v>34.77</v>
       </c>
       <c r="D33" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>45536</v>
+        <v>46631</v>
       </c>
       <c r="B34" t="n">
-        <v>25.69825872</v>
+        <v>32.18394035</v>
       </c>
       <c r="C34" t="n">
-        <v>29.5</v>
+        <v>34.77</v>
       </c>
       <c r="D34" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45566</v>
+        <v>46661</v>
       </c>
       <c r="B35" t="n">
-        <v>26.28777553</v>
+        <v>32.41735831</v>
       </c>
       <c r="C35" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D35" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>45597</v>
+        <v>46692</v>
       </c>
       <c r="B36" t="n">
-        <v>26.12159507</v>
+        <v>32.64015681</v>
       </c>
       <c r="C36" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D36" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>45627</v>
+        <v>46722</v>
       </c>
       <c r="B37" t="n">
-        <v>26.53084596</v>
+        <v>32.85574427</v>
       </c>
       <c r="C37" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D37" t="n">
-        <v>29.5</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>45658</v>
+        <v>46753</v>
       </c>
       <c r="B38" t="n">
-        <v>25.8656134</v>
+        <v>32.06876427569971</v>
       </c>
       <c r="C38" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D38" t="n">
-        <v>29.5</v>
+        <v>34.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>45689</v>
+        <v>46784</v>
       </c>
       <c r="B39" t="n">
-        <v>26.25359514</v>
+        <v>32.51328892449581</v>
       </c>
       <c r="C39" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D39" t="n">
-        <v>29.5</v>
+        <v>34.77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>45717</v>
+        <v>46813</v>
       </c>
       <c r="B40" t="n">
-        <v>26.90295259</v>
+        <v>33.04335147635302</v>
       </c>
       <c r="C40" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D40" t="n">
-        <v>29.5</v>
+        <v>34.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>45748</v>
+        <v>46844</v>
       </c>
       <c r="B41" t="n">
-        <v>26.86164757</v>
+        <v>33.3095055897306</v>
       </c>
       <c r="C41" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D41" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>45778</v>
+        <v>46874</v>
       </c>
       <c r="B42" t="n">
-        <v>26.87649226</v>
+        <v>33.57798890137586</v>
       </c>
       <c r="C42" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D42" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>45809</v>
+        <v>46905</v>
       </c>
       <c r="B43" t="n">
-        <v>27.44590982</v>
+        <v>33.84346068132069</v>
       </c>
       <c r="C43" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
       <c r="D43" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>45839</v>
+        <v>46935</v>
       </c>
       <c r="B44" t="n">
-        <v>28.09928137</v>
+        <v>34.10682441059078</v>
       </c>
       <c r="C44" t="n">
-        <v>29.5</v>
+        <v>39.02</v>
       </c>
       <c r="D44" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>45870</v>
+        <v>46966</v>
       </c>
       <c r="B45" t="n">
-        <v>28.34933697</v>
+        <v>34.3668110051568</v>
       </c>
       <c r="C45" t="n">
-        <v>29.5</v>
+        <v>39.02</v>
       </c>
       <c r="D45" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>45901</v>
+        <v>46997</v>
       </c>
       <c r="B46" t="n">
-        <v>28.48629962</v>
+        <v>34.62276080897696</v>
       </c>
       <c r="C46" t="n">
-        <v>29.5</v>
+        <v>39.02</v>
       </c>
       <c r="D46" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>45931</v>
+        <v>47027</v>
       </c>
       <c r="B47" t="n">
-        <v>27.75974445</v>
+        <v>34.87386661235941</v>
       </c>
       <c r="C47" t="n">
-        <v>29.5</v>
+        <v>39.02</v>
       </c>
       <c r="D47" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>45962</v>
+        <v>47058</v>
       </c>
       <c r="B48" t="n">
-        <v>28.68153881</v>
+        <v>35.11354823897847</v>
       </c>
       <c r="C48" t="n">
-        <v>29.5</v>
+        <v>39.02</v>
       </c>
       <c r="D48" t="n">
-        <v>29.5</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>45992</v>
+        <v>47088</v>
       </c>
       <c r="B49" t="n">
-        <v>28.91912698</v>
+        <v>35.34547239058394</v>
       </c>
       <c r="C49" t="n">
-        <v>29.5</v>
+        <v>39.02</v>
       </c>
       <c r="D49" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B50" t="n">
-        <v>27.92296452</v>
-      </c>
-      <c r="C50" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D50" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>46054</v>
-      </c>
-      <c r="B51" t="n">
-        <v>28.93248373</v>
-      </c>
-      <c r="C51" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D51" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>46082</v>
-      </c>
-      <c r="B52" t="n">
-        <v>28.84765075</v>
-      </c>
-      <c r="C52" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D52" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B53" t="n">
-        <v>28.96837335</v>
-      </c>
-      <c r="C53" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D53" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B54" t="n">
-        <v>28.96428488</v>
-      </c>
-      <c r="C54" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D54" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B55" t="n">
-        <v>29.45638012</v>
-      </c>
-      <c r="C55" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D55" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B56" t="n">
-        <v>29.56494646</v>
-      </c>
-      <c r="C56" t="n">
-        <v>30.07</v>
-      </c>
-      <c r="D56" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B57" t="n">
-        <v>29.65626961</v>
-      </c>
-      <c r="C57" t="n">
-        <v>30.07</v>
-      </c>
-      <c r="D57" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B58" t="n">
-        <v>29.69343155</v>
-      </c>
-      <c r="C58" t="n">
-        <v>30.07</v>
-      </c>
-      <c r="D58" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B59" t="n">
-        <v>29.70331723</v>
-      </c>
-      <c r="C59" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="D59" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B60" t="n">
-        <v>29.79495856</v>
-      </c>
-      <c r="C60" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="D60" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B61" t="n">
-        <v>29.99115633</v>
-      </c>
-      <c r="C61" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D61" t="n">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>46388</v>
-      </c>
-      <c r="B62" t="n">
-        <v>29.80984683</v>
-      </c>
-      <c r="C62" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D62" t="n">
-        <v>30.07</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>46419</v>
-      </c>
-      <c r="B63" t="n">
-        <v>30.22305925</v>
-      </c>
-      <c r="C63" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D63" t="n">
-        <v>30.07</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>46447</v>
-      </c>
-      <c r="B64" t="n">
-        <v>30.7157843</v>
-      </c>
-      <c r="C64" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D64" t="n">
-        <v>30.07</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>46478</v>
-      </c>
-      <c r="B65" t="n">
-        <v>30.96319057</v>
-      </c>
-      <c r="C65" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D65" t="n">
-        <v>32.57</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>46508</v>
-      </c>
-      <c r="B66" t="n">
-        <v>31.21276197</v>
-      </c>
-      <c r="C66" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D66" t="n">
-        <v>32.57</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>46539</v>
-      </c>
-      <c r="B67" t="n">
-        <v>31.45953397</v>
-      </c>
-      <c r="C67" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D67" t="n">
-        <v>34.07</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>46569</v>
-      </c>
-      <c r="B68" t="n">
-        <v>31.70434641</v>
-      </c>
-      <c r="C68" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="D68" t="n">
-        <v>34.07</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>46600</v>
-      </c>
-      <c r="B69" t="n">
-        <v>31.9460196</v>
-      </c>
-      <c r="C69" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="D69" t="n">
-        <v>34.07</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46631</v>
-      </c>
-      <c r="B70" t="n">
-        <v>32.18394035</v>
-      </c>
-      <c r="C70" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="D70" t="n">
-        <v>34.07</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46661</v>
-      </c>
-      <c r="B71" t="n">
-        <v>32.41735831</v>
-      </c>
-      <c r="C71" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D71" t="n">
-        <v>34.07</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>46692</v>
-      </c>
-      <c r="B72" t="n">
-        <v>32.64015681</v>
-      </c>
-      <c r="C72" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D72" t="n">
-        <v>34.07</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>46722</v>
-      </c>
-      <c r="B73" t="n">
-        <v>32.85574427</v>
-      </c>
-      <c r="C73" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D73" t="n">
-        <v>34.07</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>46753</v>
-      </c>
-      <c r="B74" t="n">
-        <v>32.06876427569971</v>
-      </c>
-      <c r="C74" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D74" t="n">
-        <v>34.77</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>46784</v>
-      </c>
-      <c r="B75" t="n">
-        <v>32.51328892449581</v>
-      </c>
-      <c r="C75" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D75" t="n">
-        <v>34.77</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>46813</v>
-      </c>
-      <c r="B76" t="n">
-        <v>33.04335147635302</v>
-      </c>
-      <c r="C76" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D76" t="n">
-        <v>34.77</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>46844</v>
-      </c>
-      <c r="B77" t="n">
-        <v>33.3095055897306</v>
-      </c>
-      <c r="C77" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D77" t="n">
-        <v>36.52</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>46874</v>
-      </c>
-      <c r="B78" t="n">
-        <v>33.57798890137586</v>
-      </c>
-      <c r="C78" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D78" t="n">
-        <v>36.52</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>46905</v>
-      </c>
-      <c r="B79" t="n">
-        <v>33.84346068132069</v>
-      </c>
-      <c r="C79" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="D79" t="n">
-        <v>36.52</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>46935</v>
-      </c>
-      <c r="B80" t="n">
-        <v>34.10682441059078</v>
-      </c>
-      <c r="C80" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="D80" t="n">
-        <v>36.52</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>46966</v>
-      </c>
-      <c r="B81" t="n">
-        <v>34.3668110051568</v>
-      </c>
-      <c r="C81" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="D81" t="n">
-        <v>36.52</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>46997</v>
-      </c>
-      <c r="B82" t="n">
-        <v>34.62276080897696</v>
-      </c>
-      <c r="C82" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="D82" t="n">
-        <v>36.52</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>47027</v>
-      </c>
-      <c r="B83" t="n">
-        <v>34.87386661235941</v>
-      </c>
-      <c r="C83" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="D83" t="n">
-        <v>36.52</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>47058</v>
-      </c>
-      <c r="B84" t="n">
-        <v>35.11354823897847</v>
-      </c>
-      <c r="C84" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="D84" t="n">
-        <v>36.52</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>47088</v>
-      </c>
-      <c r="B85" t="n">
-        <v>35.34547239058394</v>
-      </c>
-      <c r="C85" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="D85" t="n">
         <v>36.52</v>
       </c>
     </row>
@@ -4395,31 +3963,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Capacity Bcf/d</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>In-service month</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Source / verification</t>
         </is>
@@ -4429,25 +4002,28 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Existing Permian takeaway (aggregate, Waha-bound + Midland/Eagle Ford routes incl. Matterhorn)</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>26.5</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>In service</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Calibration: with local demand it brackets STEO Permian marketed in 2026. Total is unverified.</t>
         </is>
@@ -4457,25 +4033,28 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Matterhorn Express (Kinder/WhiteWater/EnLink/Devon, Waha-Katy)</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>2.5</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>In service</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Already inside the existing aggregate above (shown for reference, not added).</t>
         </is>
@@ -4485,25 +4064,28 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Gulf Coast Express expansion (Kinder Morgan)</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>0.57</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Under construction</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -4513,25 +4095,28 @@
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Blackcomb Pipeline (WhiteWater/Targa/MPLX/Enterprise)</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>2.5</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Under construction</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -4541,25 +4126,28 @@
       <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Hugh Brinson Pipeline (Energy Transfer, phase 1)</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Under construction</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -4569,25 +4157,28 @@
       <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Hugh Brinson Pipeline (Energy Transfer, phase 2 expansion)</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>0.7</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Under construction</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -4597,25 +4188,28 @@
       <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Eiger Express (WhiteWater/Targa/MPLX/Enterprise)</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>2.5</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -4625,25 +4219,28 @@
       <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Traverse Pipeline (WhiteWater, Agua Dulce)</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1.75</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2027-10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>

--- a/output/Data and Chart Outputs/texas_production_forecast.xlsx
+++ b/output/Data and Chart Outputs/texas_production_forecast.xlsx
@@ -16601,56 +16601,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.5</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Capacity Bcf/d</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>In-service month</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Source / verification</t>
         </is>
@@ -16675,25 +16680,28 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Existing Permian takeaway (aggregate, Waha-bound + Midland/Eagle Ford routes incl. Matterhorn)</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>26.5</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>In service</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Calibration: with local demand it brackets STEO Permian marketed in 2026. Total is unverified.</t>
         </is>
@@ -16718,25 +16726,28 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Matterhorn Express (Kinder/WhiteWater/EnLink/Devon, Waha-Katy)</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>In service</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Already inside the existing aggregate above (shown for reference, not added).</t>
         </is>
@@ -16761,25 +16772,28 @@
       <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Gulf Coast Express expansion (Kinder Morgan)</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.57</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Under construction</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -16804,25 +16818,28 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Blackcomb Pipeline (WhiteWater/Targa/MPLX/Enterprise)</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>2.5</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Under construction</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -16847,25 +16864,28 @@
       <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Hugh Brinson Pipeline (Energy Transfer, phase 1)</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1.5</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Under construction</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -16890,25 +16910,28 @@
       <c r="F7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Hugh Brinson Pipeline (Energy Transfer, phase 2 expansion)</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.7</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Under construction</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -16933,25 +16956,28 @@
       <c r="F8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Eiger Express (WhiteWater/Targa/MPLX/Enterprise)</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2.5</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -16976,25 +17002,28 @@
       <c r="F9" t="n">
         <v>7</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Traverse Pipeline (WhiteWater, Agua Dulce)</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1.75</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2027-10</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>unverified - company announcement, date from memory</t>
         </is>
@@ -51887,12 +51916,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>67.24470205671348</v>
       </c>
     </row>
     <row r="3">
@@ -51925,12 +51952,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>51.52016755003995</v>
       </c>
     </row>
     <row r="4">
@@ -51963,12 +51988,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J4" t="n">
+        <v>54.96045488366111</v>
       </c>
     </row>
     <row r="5">
@@ -52001,12 +52024,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>59.44995085566263</v>
       </c>
     </row>
     <row r="6">
@@ -52039,12 +52060,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>69.07654575016305</v>
       </c>
     </row>
     <row r="7">
@@ -52077,12 +52096,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>67.97883578442629</v>
       </c>
     </row>
     <row r="8">
@@ -52115,12 +52132,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>66.17124275465493</v>
       </c>
     </row>
     <row r="9">
@@ -52153,12 +52168,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>62.41955485334778</v>
       </c>
     </row>
     <row r="10">
@@ -52191,12 +52204,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>70.35595197633722</v>
       </c>
     </row>
     <row r="11">
@@ -52229,12 +52240,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>79.19513516989242</v>
       </c>
     </row>
     <row r="12">
@@ -52267,12 +52276,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>80.23166732498645</v>
       </c>
     </row>
     <row r="13">
@@ -52305,12 +52312,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>544.3150000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>80.58164849397866</v>
       </c>
     </row>
     <row r="14">
@@ -52343,12 +52348,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J14" t="n">
+        <v>59.56622436146036</v>
       </c>
     </row>
     <row r="15">
@@ -52381,12 +52384,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J15" t="n">
+        <v>44.66152959554626</v>
       </c>
     </row>
     <row r="16">
@@ -52419,12 +52420,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J16" t="n">
+        <v>44.69578076352921</v>
       </c>
     </row>
     <row r="17">
@@ -52457,12 +52456,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J17" t="n">
+        <v>52.76709568217816</v>
       </c>
     </row>
     <row r="18">
@@ -52495,12 +52492,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J18" t="n">
+        <v>58.43720437980014</v>
       </c>
     </row>
     <row r="19">
@@ -52533,12 +52528,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J19" t="n">
+        <v>62.1631515423899</v>
       </c>
     </row>
     <row r="20">
@@ -52571,12 +52564,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J20" t="n">
+        <v>60.85019010304345</v>
       </c>
     </row>
     <row r="21">
@@ -52609,12 +52600,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J21" t="n">
+        <v>60.6745849084642</v>
       </c>
     </row>
     <row r="22">
@@ -52647,12 +52636,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J22" t="n">
+        <v>68.61088860940258</v>
       </c>
     </row>
     <row r="23">
@@ -52685,12 +52672,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J23" t="n">
+        <v>79.88006654512635</v>
       </c>
     </row>
     <row r="24">
@@ -52723,12 +52708,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J24" t="n">
+        <v>80.76407288068633</v>
       </c>
     </row>
     <row r="25">
@@ -52761,12 +52744,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>551.806</v>
+      </c>
+      <c r="J25" t="n">
+        <v>75.65829295078342</v>
       </c>
     </row>
     <row r="26">
@@ -52799,12 +52780,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>71.12192799418557</v>
       </c>
     </row>
     <row r="27">
@@ -52837,12 +52816,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>68.19090936962901</v>
       </c>
     </row>
     <row r="28">
@@ -52875,12 +52852,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>71.09451507079568</v>
       </c>
     </row>
     <row r="29">
@@ -52913,12 +52888,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J29" t="n">
+        <v>75.09698223390076</v>
       </c>
     </row>
     <row r="30">
@@ -52951,12 +52924,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>81.32620837789437</v>
       </c>
     </row>
     <row r="31">
@@ -52989,12 +52960,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>83.25575355781874</v>
       </c>
     </row>
     <row r="32">
@@ -53027,12 +52996,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>80.09695518167375</v>
       </c>
     </row>
     <row r="33">
@@ -53065,12 +53032,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>72.34541004863991</v>
       </c>
     </row>
     <row r="34">
@@ -53103,12 +53068,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>73.61415949632361</v>
       </c>
     </row>
     <row r="35">
@@ -53141,12 +53104,10 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J35" t="n">
+        <v>81.80629523357796</v>
       </c>
     </row>
     <row r="36">
@@ -53179,12 +53140,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>83.79697844658899</v>
       </c>
     </row>
     <row r="37">
@@ -53217,12 +53176,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>554.4829999999999</v>
+      </c>
+      <c r="J37" t="n">
+        <v>83.24962171969204</v>
       </c>
     </row>
     <row r="38">
@@ -53255,12 +53212,10 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J38" t="n">
+        <v>65.24606348146624</v>
       </c>
     </row>
     <row r="39">
@@ -53293,12 +53248,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J39" t="n">
+        <v>67.46255246915773</v>
       </c>
     </row>
     <row r="40">
@@ -53331,12 +53284,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J40" t="n">
+        <v>74.43553484804364</v>
       </c>
     </row>
     <row r="41">
@@ -53369,12 +53320,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J41" t="n">
+        <v>79.637882909437</v>
       </c>
     </row>
     <row r="42">
@@ -53407,12 +53356,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J42" t="n">
+        <v>83.28604302648495</v>
       </c>
     </row>
     <row r="43">
@@ -53445,12 +53392,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J43" t="n">
+        <v>84.49221219202114</v>
       </c>
     </row>
     <row r="44">
@@ -53483,12 +53428,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J44" t="n">
+        <v>81.56441543498796</v>
       </c>
     </row>
     <row r="45">
@@ -53521,12 +53464,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J45" t="n">
+        <v>72.47295752040172</v>
       </c>
     </row>
     <row r="46">
@@ -53559,12 +53500,10 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J46" t="n">
+        <v>73.86503263563856</v>
       </c>
     </row>
     <row r="47">
@@ -53597,12 +53536,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J47" t="n">
+        <v>83.72497283322798</v>
       </c>
     </row>
     <row r="48">
@@ -53635,12 +53572,10 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J48" t="n">
+        <v>86.63163987869061</v>
       </c>
     </row>
     <row r="49">
@@ -53673,12 +53608,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J49" t="n">
+        <v>84.15094071606639</v>
       </c>
     </row>
     <row r="50">
@@ -53711,12 +53644,10 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J50" t="n">
+        <v>63.71549109711145</v>
       </c>
     </row>
     <row r="51">
@@ -53749,12 +53680,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J51" t="n">
+        <v>49.96768397053914</v>
       </c>
     </row>
     <row r="52">
@@ -53787,12 +53716,10 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J52" t="n">
+        <v>57.80911525103518</v>
       </c>
     </row>
     <row r="53">
@@ -53825,12 +53752,10 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J53" t="n">
+        <v>65.216055739824</v>
       </c>
     </row>
     <row r="54">
@@ -53863,12 +53788,10 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J54" t="n">
+        <v>73.94706563350071</v>
       </c>
     </row>
     <row r="55">
@@ -53901,12 +53824,10 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J55" t="n">
+        <v>80.30480052842034</v>
       </c>
     </row>
     <row r="56">
@@ -53939,12 +53860,10 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J56" t="n">
+        <v>81.40319040888654</v>
       </c>
     </row>
     <row r="57">
@@ -53977,12 +53896,10 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J57" t="n">
+        <v>79.12295716528051</v>
       </c>
     </row>
     <row r="58">
@@ -54015,12 +53932,10 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J58" t="n">
+        <v>81.12424270403488</v>
       </c>
     </row>
     <row r="59">
@@ -54053,12 +53968,10 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J59" t="n">
+        <v>86.81346193455826</v>
       </c>
     </row>
     <row r="60">
@@ -54091,12 +54004,10 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J60" t="n">
+        <v>91.59339332514188</v>
       </c>
     </row>
     <row r="61">
@@ -54129,12 +54040,10 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J61" t="n">
+        <v>81.39289189400343</v>
       </c>
     </row>
     <row r="62">
@@ -54167,12 +54076,10 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J62" t="n">
+        <v>61.74918499683942</v>
       </c>
     </row>
     <row r="63">
@@ -54205,12 +54112,10 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J63" t="n">
+        <v>55.37333892057359</v>
       </c>
     </row>
     <row r="64">
@@ -54243,12 +54148,10 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J64" t="n">
+        <v>60.67245750974808</v>
       </c>
     </row>
     <row r="65">
@@ -54281,12 +54184,10 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J65" t="n">
+        <v>65.80946326981399</v>
       </c>
     </row>
     <row r="66">
@@ -54319,12 +54220,10 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J66" t="n">
+        <v>70.78755229159712</v>
       </c>
     </row>
     <row r="67">
@@ -54357,12 +54256,10 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J67" t="n">
+        <v>74.10687017479066</v>
       </c>
     </row>
     <row r="68">
@@ -54395,12 +54292,10 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J68" t="n">
+        <v>74.59409646512356</v>
       </c>
     </row>
     <row r="69">
@@ -54433,12 +54328,10 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J69" t="n">
+        <v>68.30927979052585</v>
       </c>
     </row>
     <row r="70">
@@ -54471,12 +54364,10 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J70" t="n">
+        <v>69.94609260140486</v>
       </c>
     </row>
     <row r="71">
@@ -54509,12 +54400,10 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J71" t="n">
+        <v>78.01941802737275</v>
       </c>
     </row>
     <row r="72">
@@ -54547,12 +54436,10 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J72" t="n">
+        <v>81.18413981358505</v>
       </c>
     </row>
     <row r="73">
@@ -54585,12 +54472,10 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J73" t="n">
+        <v>76.89309194561437</v>
       </c>
     </row>
     <row r="74">
@@ -54623,12 +54508,10 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J74" t="n">
+        <v>57.95785184816911</v>
       </c>
     </row>
     <row r="75">
@@ -54661,12 +54544,10 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J75" t="n">
+        <v>51.91742591171654</v>
       </c>
     </row>
     <row r="76">
@@ -54699,12 +54580,10 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J76" t="n">
+        <v>58.549669496452</v>
       </c>
     </row>
     <row r="77">
@@ -54737,12 +54616,10 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J77" t="n">
+        <v>64.47445245821018</v>
       </c>
     </row>
     <row r="78">
@@ -54775,12 +54652,10 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J78" t="n">
+        <v>70.28826004407257</v>
       </c>
     </row>
     <row r="79">
@@ -54813,12 +54688,10 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J79" t="n">
+        <v>73.94381851951357</v>
       </c>
     </row>
     <row r="80">
@@ -54851,12 +54724,10 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J80" t="n">
+        <v>73.5237693233896</v>
       </c>
     </row>
     <row r="81">
@@ -54889,12 +54760,10 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J81" t="n">
+        <v>67.23895264879188</v>
       </c>
     </row>
     <row r="82">
@@ -54927,12 +54796,10 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J82" t="n">
+        <v>68.8757654596709</v>
       </c>
     </row>
     <row r="83">
@@ -54965,12 +54832,10 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J83" t="n">
+        <v>76.9490908856388</v>
       </c>
     </row>
     <row r="84">
@@ -55003,12 +54868,10 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J84" t="n">
+        <v>80.11381267185109</v>
       </c>
     </row>
     <row r="85">
@@ -55041,12 +54904,10 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J85" t="n">
+        <v>75.82276480388042</v>
       </c>
     </row>
     <row r="86">
@@ -55079,12 +54940,10 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J86" t="n">
+        <v>56.88752470643516</v>
       </c>
     </row>
     <row r="87">
@@ -55117,12 +54976,10 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J87" t="n">
+        <v>50.63136927225212</v>
       </c>
     </row>
     <row r="88">
@@ -55155,12 +55012,10 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J88" t="n">
+        <v>57.26361285698759</v>
       </c>
     </row>
     <row r="89">
@@ -55193,12 +55048,10 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J89" t="n">
+        <v>63.18839581874577</v>
       </c>
     </row>
     <row r="90">
@@ -55231,12 +55084,10 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J90" t="n">
+        <v>69.00220340460815</v>
       </c>
     </row>
     <row r="91">
@@ -55269,12 +55120,10 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J91" t="n">
+        <v>72.65776188004916</v>
       </c>
     </row>
     <row r="92">
@@ -55307,12 +55156,10 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J92" t="n">
+        <v>72.23771268392518</v>
       </c>
     </row>
     <row r="93">
@@ -55345,12 +55192,10 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J93" t="n">
+        <v>65.95289600932747</v>
       </c>
     </row>
     <row r="94">
@@ -55383,12 +55228,10 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J94" t="n">
+        <v>67.5897088202065</v>
       </c>
     </row>
     <row r="95">
@@ -55421,12 +55264,10 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J95" t="n">
+        <v>75.66303424617438</v>
       </c>
     </row>
     <row r="96">
@@ -55459,12 +55300,10 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J96" t="n">
+        <v>78.82775603238667</v>
       </c>
     </row>
     <row r="97">
@@ -55497,12 +55336,10 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J97" t="n">
+        <v>74.53670816441601</v>
       </c>
     </row>
     <row r="98">
@@ -55535,12 +55372,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J98" t="n">
+        <v>55.60146806697074</v>
       </c>
     </row>
     <row r="99">
@@ -55573,12 +55408,10 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J99" t="n">
+        <v>49.56104213051817</v>
       </c>
     </row>
     <row r="100">
@@ -55611,12 +55444,10 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J100" t="n">
+        <v>56.19328571525364</v>
       </c>
     </row>
     <row r="101">
@@ -55649,12 +55480,10 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J101" t="n">
+        <v>62.11806867701182</v>
       </c>
     </row>
     <row r="102">
@@ -55687,12 +55516,10 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J102" t="n">
+        <v>67.9318762628742</v>
       </c>
     </row>
     <row r="103">
@@ -55725,12 +55552,10 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J103" t="n">
+        <v>71.58743473831521</v>
       </c>
     </row>
     <row r="104">
@@ -55763,12 +55588,10 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J104" t="n">
+        <v>71.16738554219123</v>
       </c>
     </row>
     <row r="105">
@@ -55801,12 +55624,10 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J105" t="n">
+        <v>64.88256886759352</v>
       </c>
     </row>
     <row r="106">
@@ -55839,12 +55660,10 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J106" t="n">
+        <v>66.51938167847253</v>
       </c>
     </row>
     <row r="107">
@@ -55877,12 +55696,10 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J107" t="n">
+        <v>74.59270710444042</v>
       </c>
     </row>
     <row r="108">
@@ -55915,12 +55732,10 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J108" t="n">
+        <v>77.75742889065272</v>
       </c>
     </row>
     <row r="109">
@@ -55953,12 +55768,10 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J109" t="n">
+        <v>73.46638102268204</v>
       </c>
     </row>
     <row r="110">
@@ -55991,12 +55804,10 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J110" t="n">
+        <v>54.53114092523678</v>
       </c>
     </row>
     <row r="111">
@@ -56029,12 +55840,10 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J111" t="n">
+        <v>48.49071498878421</v>
       </c>
     </row>
     <row r="112">
@@ -56067,12 +55876,10 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J112" t="n">
+        <v>55.12295857351967</v>
       </c>
     </row>
     <row r="113">
@@ -56105,12 +55912,10 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J113" t="n">
+        <v>61.04774153527786</v>
       </c>
     </row>
     <row r="114">
@@ -56143,12 +55948,10 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J114" t="n">
+        <v>66.86154912114024</v>
       </c>
     </row>
     <row r="115">
@@ -56181,12 +55984,10 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J115" t="n">
+        <v>70.51710759658125</v>
       </c>
     </row>
     <row r="116">
@@ -56219,12 +56020,10 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J116" t="n">
+        <v>70.09705840045727</v>
       </c>
     </row>
     <row r="117">
@@ -56257,12 +56056,10 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J117" t="n">
+        <v>63.81224172585956</v>
       </c>
     </row>
     <row r="118">
@@ -56295,12 +56092,10 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J118" t="n">
+        <v>65.44905453673859</v>
       </c>
     </row>
     <row r="119">
@@ -56333,12 +56128,10 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J119" t="n">
+        <v>73.52237996270647</v>
       </c>
     </row>
     <row r="120">
@@ -56371,12 +56164,10 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J120" t="n">
+        <v>76.68710174891876</v>
       </c>
     </row>
     <row r="121">
@@ -56409,12 +56200,10 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J121" t="n">
+        <v>72.39605388094809</v>
       </c>
     </row>
     <row r="122">
@@ -56447,12 +56236,10 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J122" t="n">
+        <v>53.46081378350283</v>
       </c>
     </row>
     <row r="123">
@@ -56485,12 +56272,10 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J123" t="n">
+        <v>47.42038784705026</v>
       </c>
     </row>
     <row r="124">
@@ -56523,12 +56308,10 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J124" t="n">
+        <v>54.05263143178573</v>
       </c>
     </row>
     <row r="125">
@@ -56561,12 +56344,10 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J125" t="n">
+        <v>59.9774143935439</v>
       </c>
     </row>
     <row r="126">
@@ -56599,12 +56380,10 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J126" t="n">
+        <v>65.79122197940629</v>
       </c>
     </row>
     <row r="127">
@@ -56637,12 +56416,10 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J127" t="n">
+        <v>69.44678045484729</v>
       </c>
     </row>
     <row r="128">
@@ -56675,12 +56452,10 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J128" t="n">
+        <v>69.02673125872332</v>
       </c>
     </row>
     <row r="129">
@@ -56713,12 +56488,10 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J129" t="n">
+        <v>62.74191458412561</v>
       </c>
     </row>
     <row r="130">
@@ -56751,12 +56524,10 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J130" t="n">
+        <v>64.37872739500462</v>
       </c>
     </row>
     <row r="131">
@@ -56789,12 +56560,10 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J131" t="n">
+        <v>72.45205282097251</v>
       </c>
     </row>
     <row r="132">
@@ -56827,12 +56596,10 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J132" t="n">
+        <v>75.61677460718481</v>
       </c>
     </row>
     <row r="133">
@@ -56865,12 +56632,10 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J133" t="n">
+        <v>71.32572673921413</v>
       </c>
     </row>
     <row r="134">
@@ -56903,12 +56668,10 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J134" t="n">
+        <v>52.39048664176887</v>
       </c>
     </row>
     <row r="135">
@@ -56941,12 +56704,10 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J135" t="n">
+        <v>46.13433120758585</v>
       </c>
     </row>
     <row r="136">
@@ -56979,12 +56740,10 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J136" t="n">
+        <v>52.76657479232132</v>
       </c>
     </row>
     <row r="137">
@@ -57017,12 +56776,10 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J137" t="n">
+        <v>58.69135775407949</v>
       </c>
     </row>
     <row r="138">
@@ -57055,12 +56812,10 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J138" t="n">
+        <v>64.50516533994188</v>
       </c>
     </row>
     <row r="139">
@@ -57093,12 +56848,10 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J139" t="n">
+        <v>68.16072381538288</v>
       </c>
     </row>
     <row r="140">
@@ -57131,12 +56884,10 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J140" t="n">
+        <v>67.7406746192589</v>
       </c>
     </row>
     <row r="141">
@@ -57169,12 +56920,10 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J141" t="n">
+        <v>61.4558579446612</v>
       </c>
     </row>
     <row r="142">
@@ -57207,12 +56956,10 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J142" t="n">
+        <v>63.09267075554021</v>
       </c>
     </row>
     <row r="143">
@@ -57245,12 +56992,10 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J143" t="n">
+        <v>71.16599618150809</v>
       </c>
     </row>
     <row r="144">
@@ -57283,12 +57028,10 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J144" t="n">
+        <v>74.33071796772039</v>
       </c>
     </row>
     <row r="145">
@@ -57321,12 +57064,10 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J145" t="n">
+        <v>70.03967009974973</v>
       </c>
     </row>
     <row r="146">
@@ -57359,12 +57100,10 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J146" t="n">
+        <v>51.10443000230445</v>
       </c>
     </row>
     <row r="147">
@@ -57397,12 +57136,10 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J147" t="n">
+        <v>45.06400406585189</v>
       </c>
     </row>
     <row r="148">
@@ -57435,12 +57172,10 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J148" t="n">
+        <v>51.69624765058736</v>
       </c>
     </row>
     <row r="149">
@@ -57473,12 +57208,10 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J149" t="n">
+        <v>57.62103061234554</v>
       </c>
     </row>
     <row r="150">
@@ -57511,12 +57244,10 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J150" t="n">
+        <v>63.43483819820792</v>
       </c>
     </row>
     <row r="151">
@@ -57549,12 +57280,10 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J151" t="n">
+        <v>67.09039667364893</v>
       </c>
     </row>
     <row r="152">
@@ -57587,12 +57316,10 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J152" t="n">
+        <v>66.67034747752496</v>
       </c>
     </row>
     <row r="153">
@@ -57625,12 +57352,10 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J153" t="n">
+        <v>60.38553080292724</v>
       </c>
     </row>
     <row r="154">
@@ -57663,12 +57388,10 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J154" t="n">
+        <v>62.02234361380625</v>
       </c>
     </row>
     <row r="155">
@@ -57701,12 +57424,10 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J155" t="n">
+        <v>70.09566903977415</v>
       </c>
     </row>
     <row r="156">
@@ -57739,12 +57460,10 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J156" t="n">
+        <v>73.26039082598645</v>
       </c>
     </row>
     <row r="157">
@@ -57777,12 +57496,10 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>563.188</v>
+      </c>
+      <c r="J157" t="n">
+        <v>68.96934295801577</v>
       </c>
     </row>
   </sheetData>
